--- a/src/main/resources/python/MultifacetedModeling/Results/OnTrain/KnowledgeKernel/KNN/0.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/Results/OnTrain/KnowledgeKernel/KNN/0.xlsx
@@ -442,56 +442,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1.083984375</t>
+          <t>1.298828125</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>1.103515625</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1.298828125</t>
+          <t>1.474609375</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1.083984375</t>
+          <t>1.044921875</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0.673828125</t>
+          <t>1.11328125</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.376953125</t>
+          <t>1.474609375</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0.91796875</t>
+          <t>1.46484375</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1.044921875</t>
+          <t>1.220703125</t>
         </is>
       </c>
     </row>
@@ -505,91 +505,91 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>0.78125</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0.908203125</t>
+          <t>1.455078125</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1.50390625</t>
+          <t>1.171875</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1.005859375</t>
+          <t>0.64453125</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0.791015625</t>
+          <t>1.484375</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1.34765625</t>
+          <t>0.830078125</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1.15234375</t>
+          <t>1.328125</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1.357421875</t>
+          <t>0.908203125</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1.23046875</t>
+          <t>0.869140625</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1.259765625</t>
+          <t>1.044921875</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>1.298828125</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0.64453125</t>
+          <t>1.240234375</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1.2109375</t>
+          <t>0.68359375</t>
         </is>
       </c>
     </row>
@@ -617,154 +617,154 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.99609375</t>
+          <t>1.3330078125</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.4615885416666667</t>
+          <t>1.396484375</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1.3899739583333333</t>
+          <t>1.494140625</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1.2955729166666667</t>
+          <t>1.0400390625</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0.9114583333333334</t>
+          <t>1.0791015625</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>1.416015625</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>1.4892578125</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>1.2158203125</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>0.9375</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1.4615885416666667</t>
+          <t>0.9423828125</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>1.3525390625</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>1.396484375</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>0.6787109375</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>1.4892578125</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>0.68359375</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>1.1279296875</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>0.830078125</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1.1979166666666667</t>
+          <t>0.9423828125</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1.3020833333333333</t>
+          <t>1.03515625</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.416015625</t>
+          <t>1.318359375</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0.9114583333333334</t>
+          <t>1.181640625</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1.416015625</t>
+          <t>0.6884765625</t>
         </is>
       </c>
     </row>
@@ -802,17 +802,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.18790015400396384</t>
+          <t>0.07308174062497812</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.19083079135600542</t>
+          <t>0.1229284467964298</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.42140505688016194</t>
+          <t>0.7755739264028093</t>
         </is>
       </c>
     </row>
